--- a/SGC-CKN/Excel/72488967-c8cf-4ee5-8436-1f8d2e8df0f2_Lô_CT-02_P1-160_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/72488967-c8cf-4ee5-8436-1f8d2e8df0f2_Lô_CT-02_P1-160_D800_29-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,7 +106,7 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Length calculated: 1.5 - 0.71 = 0.79</t>
+    <t>-</t>
   </si>
   <si>
     <t>2</t>
@@ -119,9 +119,6 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Length calculated: 9.7 - 1.5 = 8.2</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Anomalous depth recording in original document (9.7 to 7.8)</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -145,9 +139,6 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Length calculated: 16.8 - 7.8 = 9.0</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -158,9 +149,6 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Length calculated: 21.9 - 16.8 = 5.1</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -171,9 +159,6 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Length calculated: 25.9 - 21.9 = 4.0</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -184,7 +169,7 @@
 29/03/2026</t>
   </si>
   <si>
-    <t>Length calculated: 39.0 - 25.9 = 13.1</t>
+    <t>chạm sỏi CĐ 35,56m</t>
   </si>
   <si>
     <t>8</t>
@@ -195,9 +180,6 @@
   <si>
     <t xml:space="preserve">04:25
 29/03/2026</t>
-  </si>
-  <si>
-    <t>Length calculated: 44.1 - 39.0 = 5.1. Note NT đáy cọc @ 43.5/43.56</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -237,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -268,18 +250,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -326,7 +302,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,7 +331,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -365,22 +341,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFECACA"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -496,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -534,6 +505,12 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -543,7 +520,7 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -582,22 +559,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1183,7 +1151,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.5</v>
@@ -1192,10 +1160,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>0.79</v>
+        <v>1.5</v>
       </c>
       <c r="J11" s="8">
-        <v>0.79</v>
+        <v>1.5</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1221,245 +1189,245 @@
         <v>-1.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.7</v>
+        <v>-4.7</v>
       </c>
       <c r="H12" s="9">
         <v>1.17</v>
       </c>
       <c r="I12" s="9">
-        <v>8.2</v>
-      </c>
-      <c r="J12" s="12">
-        <v>7.03</v>
+        <v>3.2</v>
+      </c>
+      <c r="J12" s="8">
+        <v>2.74</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="B13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="D13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="12">
+        <v>-4.7</v>
+      </c>
+      <c r="G13" s="12">
+        <v>-7.8</v>
+      </c>
+      <c r="H13" s="12">
+        <v>1</v>
+      </c>
+      <c r="I13" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="13">
-        <v>-9.7</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="E14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="15">
         <v>-7.8</v>
       </c>
-      <c r="H13" s="13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="13">
-        <v>1.9</v>
-      </c>
-      <c r="J13" s="16">
-        <v>1.9</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="G14" s="15">
+        <v>-16.8</v>
+      </c>
+      <c r="H14" s="15">
+        <v>1.08</v>
+      </c>
+      <c r="I14" s="15">
+        <v>9</v>
+      </c>
+      <c r="J14" s="18">
+        <v>8.31</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="E15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="19">
+        <v>-16.8</v>
+      </c>
+      <c r="G15" s="19">
+        <v>-21.9</v>
+      </c>
+      <c r="H15" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="I15" s="19">
+        <v>5.1</v>
+      </c>
+      <c r="J15" s="8">
+        <v>4.71</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="17">
-        <v>-7.8</v>
-      </c>
-      <c r="G14" s="17">
-        <v>-16.8</v>
-      </c>
-      <c r="H14" s="17">
+      <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="22">
+        <v>-21.9</v>
+      </c>
+      <c r="G16" s="22">
+        <v>-25.9</v>
+      </c>
+      <c r="H16" s="22">
         <v>1.08</v>
       </c>
-      <c r="I14" s="17">
-        <v>9</v>
-      </c>
-      <c r="J14" s="12">
-        <v>8.31</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="20" t="s">
+      <c r="I16" s="22">
+        <v>4</v>
+      </c>
+      <c r="J16" s="8">
+        <v>3.69</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="22" t="s">
+      <c r="C17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="20">
-        <v>-16.8</v>
-      </c>
-      <c r="G15" s="20">
-        <v>-21.9</v>
-      </c>
-      <c r="H15" s="20">
+      <c r="E17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="25">
+        <v>-25.9</v>
+      </c>
+      <c r="G17" s="25">
+        <v>-39</v>
+      </c>
+      <c r="H17" s="25">
+        <v>0.92</v>
+      </c>
+      <c r="I17" s="25">
+        <v>13.1</v>
+      </c>
+      <c r="J17" s="18">
+        <v>14.29</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="28">
+        <v>-39</v>
+      </c>
+      <c r="G18" s="28">
+        <v>-44</v>
+      </c>
+      <c r="H18" s="28">
         <v>1.08</v>
       </c>
-      <c r="I15" s="20">
-        <v>5.1</v>
-      </c>
-      <c r="J15" s="16">
-        <v>4.71</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="23">
-        <v>-21.9</v>
-      </c>
-      <c r="G16" s="23">
-        <v>-25.9</v>
-      </c>
-      <c r="H16" s="23">
-        <v>1.08</v>
-      </c>
-      <c r="I16" s="23">
-        <v>4</v>
-      </c>
-      <c r="J16" s="16">
-        <v>3.69</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="28" t="s">
+      <c r="I18" s="28">
+        <v>5</v>
+      </c>
+      <c r="J18" s="8">
+        <v>4.62</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="26">
-        <v>-25.9</v>
-      </c>
-      <c r="G17" s="26">
-        <v>-39</v>
-      </c>
-      <c r="H17" s="26">
-        <v>0.92</v>
-      </c>
-      <c r="I17" s="26">
-        <v>13.1</v>
-      </c>
-      <c r="J17" s="12">
-        <v>14.29</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="29">
-        <v>-39</v>
-      </c>
-      <c r="G18" s="29">
-        <v>-44.1</v>
-      </c>
-      <c r="H18" s="29">
-        <v>1.08</v>
-      </c>
-      <c r="I18" s="29">
-        <v>5.1</v>
-      </c>
-      <c r="J18" s="16">
-        <v>4.71</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1554,31 +1522,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1595,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.5</v>
@@ -1604,10 +1572,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>0.79</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="8">
-        <v>0.79</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1627,219 +1595,219 @@
         <v>-1.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.7</v>
+        <v>-4.7</v>
       </c>
       <c r="G3" s="9">
         <v>1.17</v>
       </c>
       <c r="H3" s="9">
-        <v>8.2</v>
-      </c>
-      <c r="I3" s="12">
-        <v>7.03</v>
+        <v>3.2</v>
+      </c>
+      <c r="I3" s="8">
+        <v>2.74</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-9.7</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
+        <v>-4.7</v>
+      </c>
+      <c r="F4" s="12">
         <v>-7.8</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>1</v>
       </c>
-      <c r="H4" s="13">
-        <v>1.9</v>
-      </c>
-      <c r="I4" s="16">
-        <v>1.9</v>
+      <c r="H4" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="I4" s="8">
+        <v>3.1</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="17">
+      <c r="C5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="15">
         <v>-7.8</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="15">
         <v>-16.8</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="15">
         <v>1.08</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="15">
         <v>9</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="18">
         <v>8.31</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="19">
+        <v>1</v>
+      </c>
+      <c r="E6" s="19">
+        <v>-16.8</v>
+      </c>
+      <c r="F6" s="19">
+        <v>-21.9</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="H6" s="19">
+        <v>5.1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E6" s="20">
-        <v>-16.8</v>
-      </c>
-      <c r="F6" s="20">
+      <c r="E7" s="22">
         <v>-21.9</v>
       </c>
-      <c r="G6" s="20">
+      <c r="F7" s="22">
+        <v>-25.9</v>
+      </c>
+      <c r="G7" s="22">
         <v>1.08</v>
       </c>
-      <c r="H6" s="20">
-        <v>5.1</v>
-      </c>
-      <c r="I6" s="16">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
-        <v>6</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="H7" s="22">
+        <v>4</v>
+      </c>
+      <c r="I7" s="8">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="23">
+      <c r="C8" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
-        <v>-21.9</v>
-      </c>
-      <c r="F7" s="23">
+      <c r="E8" s="25">
         <v>-25.9</v>
       </c>
-      <c r="G7" s="23">
+      <c r="F8" s="25">
+        <v>-39</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0.92</v>
+      </c>
+      <c r="H8" s="25">
+        <v>13.1</v>
+      </c>
+      <c r="I8" s="18">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="28">
+        <v>1</v>
+      </c>
+      <c r="E9" s="28">
+        <v>-39</v>
+      </c>
+      <c r="F9" s="28">
+        <v>-44</v>
+      </c>
+      <c r="G9" s="28">
         <v>1.08</v>
       </c>
-      <c r="H7" s="23">
-        <v>4</v>
-      </c>
-      <c r="I7" s="16">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>7</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="26">
-        <v>1</v>
-      </c>
-      <c r="E8" s="26">
-        <v>-25.9</v>
-      </c>
-      <c r="F8" s="26">
-        <v>-39</v>
-      </c>
-      <c r="G8" s="26">
-        <v>0.92</v>
-      </c>
-      <c r="H8" s="26">
-        <v>13.1</v>
-      </c>
-      <c r="I8" s="12">
-        <v>14.29</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="H9" s="28">
+        <v>5</v>
+      </c>
+      <c r="I9" s="8">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="29">
-        <v>1</v>
-      </c>
-      <c r="E9" s="29">
-        <v>-39</v>
-      </c>
-      <c r="F9" s="29">
-        <v>-44.1</v>
-      </c>
-      <c r="G9" s="29">
-        <v>1.08</v>
-      </c>
-      <c r="H9" s="29">
-        <v>5.1</v>
-      </c>
-      <c r="I9" s="16">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="34">
-        <v>8</v>
-      </c>
-      <c r="E10" s="34">
-        <v>-0.71</v>
-      </c>
-      <c r="F10" s="34">
-        <v>-44.1</v>
-      </c>
-      <c r="G10" s="34">
+      <c r="E10" s="33">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
+        <v>-44</v>
+      </c>
+      <c r="G10" s="33">
         <v>8.42</v>
       </c>
-      <c r="H10" s="34">
-        <v>47.19</v>
-      </c>
-      <c r="I10" s="34">
-        <v>5.61</v>
+      <c r="H10" s="33">
+        <v>44</v>
+      </c>
+      <c r="I10" s="33">
+        <v>5.23</v>
       </c>
     </row>
   </sheetData>
